--- a/signal_coodination/results_final.xlsx
+++ b/signal_coodination/results_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50a7229fe28fb870/デスクトップ/randy_utokyo/signal_coodination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_339935AB9640680E62355476585DCE3A8743FF54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FA2D28C-CDC2-4DD2-9DF8-2B9AE1D1B779}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_339935AB9640680E62355476585DCE3A8743FF54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E237184C-2F5D-4079-B744-4BC1DFD03C73}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -490,6 +490,8 @@
   <cols>
     <col min="15" max="18" width="20.08984375" customWidth="1"/>
     <col min="19" max="19" width="13.6328125" customWidth="1"/>
+    <col min="20" max="20" width="13.54296875" customWidth="1"/>
+    <col min="21" max="21" width="12.54296875" customWidth="1"/>
     <col min="22" max="22" width="18.08984375" customWidth="1"/>
     <col min="23" max="26" width="13.453125" customWidth="1"/>
     <col min="27" max="27" width="12.54296875" customWidth="1"/>

--- a/signal_coodination/results_final.xlsx
+++ b/signal_coodination/results_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hibik\github\randy_utokyo\signal_coodination\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50a7229fe28fb870/デスクトップ/randy_utokyo/signal_coodination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42FAB2E-7AFC-4F1E-8DD0-374B3A2DEE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{F42FAB2E-7AFC-4F1E-8DD0-374B3A2DEE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D66CCB79-95C7-482F-9855-ADB19D6DEB61}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="22410" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -216,14 +216,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF9FDA9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -235,22 +228,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFF9FDA9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -410,6 +390,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -698,19 +682,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH157"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="14" max="14" width="12.109375" customWidth="1"/>
-    <col min="19" max="22" width="20.109375" customWidth="1"/>
-    <col min="23" max="23" width="13.6640625" customWidth="1"/>
-    <col min="24" max="24" width="13.5546875" customWidth="1"/>
-    <col min="25" max="25" width="12.5546875" customWidth="1"/>
-    <col min="26" max="26" width="18.109375" customWidth="1"/>
-    <col min="27" max="30" width="13.44140625" customWidth="1"/>
-    <col min="31" max="31" width="12.5546875" customWidth="1"/>
-    <col min="32" max="32" width="13.44140625" customWidth="1"/>
-    <col min="33" max="33" width="12.21875" customWidth="1"/>
-    <col min="34" max="34" width="15.33203125" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="9.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="19" max="19" width="15.54296875" customWidth="1"/>
+    <col min="20" max="21" width="15.26953125" customWidth="1"/>
+    <col min="22" max="22" width="14.90625" customWidth="1"/>
+    <col min="23" max="23" width="13.6328125" customWidth="1"/>
+    <col min="24" max="24" width="13.54296875" customWidth="1"/>
+    <col min="25" max="25" width="12.54296875" customWidth="1"/>
+    <col min="26" max="26" width="18.08984375" customWidth="1"/>
+    <col min="27" max="30" width="13.453125" customWidth="1"/>
+    <col min="31" max="31" width="12.54296875" customWidth="1"/>
+    <col min="32" max="32" width="13.453125" customWidth="1"/>
+    <col min="33" max="33" width="12.1796875" customWidth="1"/>
+    <col min="34" max="34" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.2">
@@ -834,11 +827,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F2">
-        <f>C2+D2</f>
+        <f t="shared" ref="F2:F33" si="0">C2+D2</f>
         <v>916.66666666666697</v>
       </c>
       <c r="G2">
-        <f>D2+E2</f>
+        <f t="shared" ref="G2:G33" si="1">D2+E2</f>
         <v>916.66666666666674</v>
       </c>
       <c r="H2">
@@ -854,11 +847,11 @@
         <v>0.25</v>
       </c>
       <c r="L2">
-        <f>F2/(120*$B2*1000/3600)</f>
+        <f t="shared" ref="L2:L33" si="2">F2/(120*$B2*1000/3600)</f>
         <v>0.55000000000000016</v>
       </c>
       <c r="M2">
-        <f>G2/(120*$B2*1000/3600)</f>
+        <f t="shared" ref="M2:M33" si="3">G2/(120*$B2*1000/3600)</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="N2">
@@ -942,11 +935,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F3">
-        <f>C3+D3</f>
+        <f t="shared" si="0"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G3">
-        <f>D3+E3</f>
+        <f t="shared" si="1"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H3">
@@ -962,11 +955,11 @@
         <v>0.26315789473684209</v>
       </c>
       <c r="L3">
-        <f>F3/(120*$B3*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.57894736842105265</v>
       </c>
       <c r="M3">
-        <f>G3/(120*$B3*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.57894736842105265</v>
       </c>
       <c r="N3">
@@ -1050,11 +1043,11 @@
         <v>416.66666666666703</v>
       </c>
       <c r="F4">
-        <f>C4+D4</f>
+        <f t="shared" si="0"/>
         <v>916.66666666666606</v>
       </c>
       <c r="G4">
-        <f>D4+E4</f>
+        <f t="shared" si="1"/>
         <v>916.66666666666697</v>
       </c>
       <c r="H4">
@@ -1070,11 +1063,11 @@
         <v>0.27777777777777801</v>
       </c>
       <c r="L4">
-        <f>F4/(120*$B4*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.61111111111111072</v>
       </c>
       <c r="M4">
-        <f>G4/(120*$B4*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.61111111111111127</v>
       </c>
       <c r="N4">
@@ -1158,11 +1151,11 @@
         <v>416.66666666666703</v>
       </c>
       <c r="F5">
-        <f>C5+D5</f>
+        <f t="shared" si="0"/>
         <v>916.66666666666606</v>
       </c>
       <c r="G5">
-        <f>D5+E5</f>
+        <f t="shared" si="1"/>
         <v>916.66666666666697</v>
       </c>
       <c r="H5">
@@ -1178,11 +1171,11 @@
         <v>0.29411764705882382</v>
       </c>
       <c r="L5">
-        <f>F5/(120*$B5*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.64705882352941135</v>
       </c>
       <c r="M5">
-        <f>G5/(120*$B5*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.64705882352941191</v>
       </c>
       <c r="N5">
@@ -1266,11 +1259,11 @@
         <v>416.66666666666703</v>
       </c>
       <c r="F6">
-        <f>C6+D6</f>
+        <f t="shared" si="0"/>
         <v>916.66666666666606</v>
       </c>
       <c r="G6">
-        <f>D6+E6</f>
+        <f t="shared" si="1"/>
         <v>916.66666666666697</v>
       </c>
       <c r="H6">
@@ -1286,11 +1279,11 @@
         <v>0.31250000000000028</v>
       </c>
       <c r="L6">
-        <f>F6/(120*$B6*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.68749999999999956</v>
       </c>
       <c r="M6">
-        <f>G6/(120*$B6*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.68750000000000022</v>
       </c>
       <c r="N6">
@@ -1374,11 +1367,11 @@
         <v>416.66666666666703</v>
       </c>
       <c r="F7">
-        <f>C7+D7</f>
+        <f t="shared" si="0"/>
         <v>916.66666666666492</v>
       </c>
       <c r="G7">
-        <f>D7+E7</f>
+        <f t="shared" si="1"/>
         <v>916.66666666666697</v>
       </c>
       <c r="H7">
@@ -1394,11 +1387,11 @@
         <v>0.33333333333333359</v>
       </c>
       <c r="L7">
-        <f>F7/(120*$B7*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.73333333333333195</v>
       </c>
       <c r="M7">
-        <f>G7/(120*$B7*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.73333333333333361</v>
       </c>
       <c r="N7">
@@ -1482,11 +1475,11 @@
         <v>416.66666666666703</v>
       </c>
       <c r="F8">
-        <f>C8+D8</f>
+        <f t="shared" si="0"/>
         <v>916.66666666666492</v>
       </c>
       <c r="G8">
-        <f>D8+E8</f>
+        <f t="shared" si="1"/>
         <v>916.66666666666697</v>
       </c>
       <c r="H8">
@@ -1502,11 +1495,11 @@
         <v>0.35714285714285737</v>
       </c>
       <c r="L8">
-        <f>F8/(120*$B8*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.78571428571428414</v>
       </c>
       <c r="M8">
-        <f>G8/(120*$B8*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.78571428571428592</v>
       </c>
       <c r="N8">
@@ -1590,11 +1583,11 @@
         <v>416.66666666666703</v>
       </c>
       <c r="F9">
-        <f>C9+D9</f>
+        <f t="shared" si="0"/>
         <v>916.66666666666492</v>
       </c>
       <c r="G9">
-        <f>D9+E9</f>
+        <f t="shared" si="1"/>
         <v>916.66666666666697</v>
       </c>
       <c r="H9">
@@ -1610,11 +1603,11 @@
         <v>0.38461538461538503</v>
       </c>
       <c r="L9">
-        <f>F9/(120*$B9*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.84615384615384459</v>
       </c>
       <c r="M9">
-        <f>G9/(120*$B9*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.84615384615384648</v>
       </c>
       <c r="N9">
@@ -1698,11 +1691,11 @@
         <v>416.66666666666703</v>
       </c>
       <c r="F10">
-        <f>C10+D10</f>
+        <f t="shared" si="0"/>
         <v>916.66666666666401</v>
       </c>
       <c r="G10">
-        <f>D10+E10</f>
+        <f t="shared" si="1"/>
         <v>916.66666666666697</v>
       </c>
       <c r="H10">
@@ -1718,11 +1711,11 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="L10">
-        <f>F10/(120*$B10*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.91666666666666397</v>
       </c>
       <c r="M10">
-        <f>G10/(120*$B10*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.91666666666666696</v>
       </c>
       <c r="N10">
@@ -1806,11 +1799,11 @@
         <v>416.66666666666703</v>
       </c>
       <c r="F11">
-        <f>C11+D11</f>
+        <f t="shared" si="0"/>
         <v>916.66666666666401</v>
       </c>
       <c r="G11">
-        <f>D11+E11</f>
+        <f t="shared" si="1"/>
         <v>916.66666666666697</v>
       </c>
       <c r="H11">
@@ -1826,11 +1819,11 @@
         <v>0.45454545454545497</v>
       </c>
       <c r="L11">
-        <f>F11/(120*$B11*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.99999999999999711</v>
       </c>
       <c r="M11">
-        <f>G11/(120*$B11*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000004</v>
       </c>
       <c r="N11">
@@ -1914,11 +1907,11 @@
         <v>416.66666666666703</v>
       </c>
       <c r="F12">
-        <f>C12+D12</f>
+        <f t="shared" si="0"/>
         <v>916.66666666666401</v>
       </c>
       <c r="G12">
-        <f>D12+E12</f>
+        <f t="shared" si="1"/>
         <v>916.66666666666697</v>
       </c>
       <c r="H12">
@@ -1934,11 +1927,11 @@
         <v>0.50000000000000044</v>
       </c>
       <c r="L12">
-        <f>F12/(120*$B12*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>1.0999999999999968</v>
       </c>
       <c r="M12">
-        <f>G12/(120*$B12*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="N12">
@@ -2022,11 +2015,11 @@
         <v>416.66666666666703</v>
       </c>
       <c r="F13">
-        <f>C13+D13</f>
+        <f t="shared" si="0"/>
         <v>916.66666666666299</v>
       </c>
       <c r="G13">
-        <f>D13+E13</f>
+        <f t="shared" si="1"/>
         <v>916.66666666666697</v>
       </c>
       <c r="H13">
@@ -2042,11 +2035,11 @@
         <v>0.55555555555555602</v>
       </c>
       <c r="L13">
-        <f>F13/(120*$B13*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>1.2222222222222172</v>
       </c>
       <c r="M13">
-        <f>G13/(120*$B13*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>1.2222222222222225</v>
       </c>
       <c r="N13">
@@ -2130,11 +2123,11 @@
         <v>416.66666666666703</v>
       </c>
       <c r="F14">
-        <f>C14+D14</f>
+        <f t="shared" si="0"/>
         <v>916.66666666666299</v>
       </c>
       <c r="G14">
-        <f>D14+E14</f>
+        <f t="shared" si="1"/>
         <v>916.66666666666697</v>
       </c>
       <c r="H14">
@@ -2150,11 +2143,11 @@
         <v>0.62500000000000056</v>
       </c>
       <c r="L14">
-        <f>F14/(120*$B14*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>1.3749999999999947</v>
       </c>
       <c r="M14">
-        <f>G14/(120*$B14*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>1.3750000000000004</v>
       </c>
       <c r="N14">
@@ -2238,11 +2231,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F15">
-        <f>C15+D15</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G15">
-        <f>D15+E15</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H15">
@@ -2258,11 +2251,11 @@
         <v>0.35</v>
       </c>
       <c r="L15">
-        <f>F15/(120*$B15*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.65</v>
       </c>
       <c r="M15">
-        <f>G15/(120*$B15*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
       <c r="N15">
@@ -2346,11 +2339,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F16">
-        <f>C16+D16</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G16">
-        <f>D16+E16</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H16">
@@ -2366,11 +2359,11 @@
         <v>0.36842105263157898</v>
       </c>
       <c r="L16">
-        <f>F16/(120*$B16*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.6842105263157896</v>
       </c>
       <c r="M16">
-        <f>G16/(120*$B16*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.6842105263157896</v>
       </c>
       <c r="N16">
@@ -2454,11 +2447,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F17">
-        <f>C17+D17</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G17">
-        <f>D17+E17</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H17">
@@ -2474,11 +2467,11 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="L17">
-        <f>F17/(120*$B17*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.72222222222222232</v>
       </c>
       <c r="M17">
-        <f>G17/(120*$B17*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.72222222222222232</v>
       </c>
       <c r="N17">
@@ -2562,11 +2555,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F18">
-        <f>C18+D18</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G18">
-        <f>D18+E18</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H18">
@@ -2582,11 +2575,11 @@
         <v>0.41176470588235292</v>
       </c>
       <c r="L18">
-        <f>F18/(120*$B18*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.76470588235294124</v>
       </c>
       <c r="M18">
-        <f>G18/(120*$B18*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.76470588235294124</v>
       </c>
       <c r="N18">
@@ -2670,11 +2663,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F19">
-        <f>C19+D19</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G19">
-        <f>D19+E19</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H19">
@@ -2690,11 +2683,11 @@
         <v>0.43750000000000011</v>
       </c>
       <c r="L19">
-        <f>F19/(120*$B19*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.81250000000000011</v>
       </c>
       <c r="M19">
-        <f>G19/(120*$B19*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.81250000000000011</v>
       </c>
       <c r="N19">
@@ -2778,11 +2771,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F20">
-        <f>C20+D20</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G20">
-        <f>D20+E20</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H20">
@@ -2798,11 +2791,11 @@
         <v>0.46666666666666667</v>
       </c>
       <c r="L20">
-        <f>F20/(120*$B20*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.86666666666666681</v>
       </c>
       <c r="M20">
-        <f>G20/(120*$B20*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.86666666666666681</v>
       </c>
       <c r="N20">
@@ -2886,11 +2879,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F21">
-        <f>C21+D21</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G21">
-        <f>D21+E21</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H21">
@@ -2906,11 +2899,11 @@
         <v>0.5</v>
       </c>
       <c r="L21">
-        <f>F21/(120*$B21*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.9285714285714286</v>
       </c>
       <c r="M21">
-        <f>G21/(120*$B21*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.9285714285714286</v>
       </c>
       <c r="N21">
@@ -2994,11 +2987,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F22">
-        <f>C22+D22</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G22">
-        <f>D22+E22</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H22">
@@ -3014,11 +3007,11 @@
         <v>0.53846153846153855</v>
       </c>
       <c r="L22">
-        <f>F22/(120*$B22*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="M22">
-        <f>G22/(120*$B22*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="N22">
@@ -3102,11 +3095,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F23">
-        <f>C23+D23</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G23">
-        <f>D23+E23</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H23">
@@ -3122,11 +3115,11 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="L23">
-        <f>F23/(120*$B23*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>1.0833333333333335</v>
       </c>
       <c r="M23">
-        <f>G23/(120*$B23*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>1.0833333333333335</v>
       </c>
       <c r="N23">
@@ -3210,11 +3203,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F24">
-        <f>C24+D24</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G24">
-        <f>D24+E24</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H24">
@@ -3230,11 +3223,11 @@
         <v>0.63636363636363646</v>
       </c>
       <c r="L24">
-        <f>F24/(120*$B24*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>1.1818181818181821</v>
       </c>
       <c r="M24">
-        <f>G24/(120*$B24*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>1.1818181818181821</v>
       </c>
       <c r="N24">
@@ -3318,11 +3311,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F25">
-        <f>C25+D25</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G25">
-        <f>D25+E25</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H25">
@@ -3338,11 +3331,11 @@
         <v>0.70000000000000007</v>
       </c>
       <c r="L25">
-        <f>F25/(120*$B25*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>1.3</v>
       </c>
       <c r="M25">
-        <f>G25/(120*$B25*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>1.3</v>
       </c>
       <c r="N25">
@@ -3426,11 +3419,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F26">
-        <f>C26+D26</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G26">
-        <f>D26+E26</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H26">
@@ -3446,11 +3439,11 @@
         <v>0.77777777777777779</v>
       </c>
       <c r="L26">
-        <f>F26/(120*$B26*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>1.4444444444444446</v>
       </c>
       <c r="M26">
-        <f>G26/(120*$B26*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>1.4444444444444446</v>
       </c>
       <c r="N26">
@@ -3534,11 +3527,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F27">
-        <f>C27+D27</f>
+        <f t="shared" si="0"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="G27">
-        <f>D27+E27</f>
+        <f t="shared" si="1"/>
         <v>1083.3333333333335</v>
       </c>
       <c r="H27">
@@ -3554,11 +3547,11 @@
         <v>0.87500000000000011</v>
       </c>
       <c r="L27">
-        <f>F27/(120*$B27*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>1.6250000000000002</v>
       </c>
       <c r="M27">
-        <f>G27/(120*$B27*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>1.6250000000000002</v>
       </c>
       <c r="N27">
@@ -3642,11 +3635,11 @@
         <v>750</v>
       </c>
       <c r="F28">
-        <f>C28+D28</f>
+        <f t="shared" si="0"/>
         <v>1250</v>
       </c>
       <c r="G28">
-        <f>D28+E28</f>
+        <f t="shared" si="1"/>
         <v>1250</v>
       </c>
       <c r="H28">
@@ -3662,11 +3655,11 @@
         <v>0.45</v>
       </c>
       <c r="L28">
-        <f>F28/(120*$B28*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
       <c r="M28">
-        <f>G28/(120*$B28*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.75</v>
       </c>
       <c r="N28">
@@ -3750,11 +3743,11 @@
         <v>750</v>
       </c>
       <c r="F29">
-        <f>C29+D29</f>
+        <f t="shared" si="0"/>
         <v>1250</v>
       </c>
       <c r="G29">
-        <f>D29+E29</f>
+        <f t="shared" si="1"/>
         <v>1250</v>
       </c>
       <c r="H29">
@@ -3770,11 +3763,11 @@
         <v>0.47368421052631582</v>
       </c>
       <c r="L29">
-        <f>F29/(120*$B29*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.78947368421052633</v>
       </c>
       <c r="M29">
-        <f>G29/(120*$B29*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.78947368421052633</v>
       </c>
       <c r="N29">
@@ -3858,11 +3851,11 @@
         <v>750</v>
       </c>
       <c r="F30">
-        <f>C30+D30</f>
+        <f t="shared" si="0"/>
         <v>1250</v>
       </c>
       <c r="G30">
-        <f>D30+E30</f>
+        <f t="shared" si="1"/>
         <v>1250</v>
       </c>
       <c r="H30">
@@ -3878,11 +3871,11 @@
         <v>0.5</v>
       </c>
       <c r="L30">
-        <f>F30/(120*$B30*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="M30">
-        <f>G30/(120*$B30*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="N30">
@@ -3966,11 +3959,11 @@
         <v>750</v>
       </c>
       <c r="F31">
-        <f>C31+D31</f>
+        <f t="shared" si="0"/>
         <v>1250</v>
       </c>
       <c r="G31">
-        <f>D31+E31</f>
+        <f t="shared" si="1"/>
         <v>1250</v>
       </c>
       <c r="H31">
@@ -3986,11 +3979,11 @@
         <v>0.52941176470588236</v>
       </c>
       <c r="L31">
-        <f>F31/(120*$B31*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.88235294117647056</v>
       </c>
       <c r="M31">
-        <f>G31/(120*$B31*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.88235294117647056</v>
       </c>
       <c r="N31">
@@ -4074,11 +4067,11 @@
         <v>750</v>
       </c>
       <c r="F32">
-        <f>C32+D32</f>
+        <f t="shared" si="0"/>
         <v>1250</v>
       </c>
       <c r="G32">
-        <f>D32+E32</f>
+        <f t="shared" si="1"/>
         <v>1250</v>
       </c>
       <c r="H32">
@@ -4094,11 +4087,11 @@
         <v>0.5625</v>
       </c>
       <c r="L32">
-        <f>F32/(120*$B32*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>0.9375</v>
       </c>
       <c r="M32">
-        <f>G32/(120*$B32*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>0.9375</v>
       </c>
       <c r="N32">
@@ -4182,11 +4175,11 @@
         <v>750</v>
       </c>
       <c r="F33">
-        <f>C33+D33</f>
+        <f t="shared" si="0"/>
         <v>1250</v>
       </c>
       <c r="G33">
-        <f>D33+E33</f>
+        <f t="shared" si="1"/>
         <v>1250</v>
       </c>
       <c r="H33">
@@ -4202,11 +4195,11 @@
         <v>0.6</v>
       </c>
       <c r="L33">
-        <f>F33/(120*$B33*1000/3600)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M33">
-        <f>G33/(120*$B33*1000/3600)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N33">
@@ -4290,11 +4283,11 @@
         <v>750</v>
       </c>
       <c r="F34">
-        <f>C34+D34</f>
+        <f t="shared" ref="F34:F65" si="4">C34+D34</f>
         <v>1250</v>
       </c>
       <c r="G34">
-        <f>D34+E34</f>
+        <f t="shared" ref="G34:G65" si="5">D34+E34</f>
         <v>1250</v>
       </c>
       <c r="H34">
@@ -4310,11 +4303,11 @@
         <v>0.64285714285714279</v>
       </c>
       <c r="L34">
-        <f>F34/(120*$B34*1000/3600)</f>
+        <f t="shared" ref="L34:L65" si="6">F34/(120*$B34*1000/3600)</f>
         <v>1.0714285714285714</v>
       </c>
       <c r="M34">
-        <f>G34/(120*$B34*1000/3600)</f>
+        <f t="shared" ref="M34:M65" si="7">G34/(120*$B34*1000/3600)</f>
         <v>1.0714285714285714</v>
       </c>
       <c r="N34">
@@ -4398,11 +4391,11 @@
         <v>750</v>
       </c>
       <c r="F35">
-        <f>C35+D35</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G35">
-        <f>D35+E35</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H35">
@@ -4418,11 +4411,11 @@
         <v>0.6923076923076924</v>
       </c>
       <c r="L35">
-        <f>F35/(120*$B35*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.153846153846154</v>
       </c>
       <c r="M35">
-        <f>G35/(120*$B35*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.153846153846154</v>
       </c>
       <c r="N35">
@@ -4506,11 +4499,11 @@
         <v>750</v>
       </c>
       <c r="F36">
-        <f>C36+D36</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G36">
-        <f>D36+E36</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H36">
@@ -4526,11 +4519,11 @@
         <v>0.75</v>
       </c>
       <c r="L36">
-        <f>F36/(120*$B36*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.25</v>
       </c>
       <c r="M36">
-        <f>G36/(120*$B36*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.25</v>
       </c>
       <c r="N36">
@@ -4614,11 +4607,11 @@
         <v>750</v>
       </c>
       <c r="F37">
-        <f>C37+D37</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G37">
-        <f>D37+E37</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H37">
@@ -4634,11 +4627,11 @@
         <v>0.81818181818181823</v>
       </c>
       <c r="L37">
-        <f>F37/(120*$B37*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.3636363636363638</v>
       </c>
       <c r="M37">
-        <f>G37/(120*$B37*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.3636363636363638</v>
       </c>
       <c r="N37">
@@ -4722,11 +4715,11 @@
         <v>750</v>
       </c>
       <c r="F38">
-        <f>C38+D38</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G38">
-        <f>D38+E38</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H38">
@@ -4742,11 +4735,11 @@
         <v>0.89999999999999991</v>
       </c>
       <c r="L38">
-        <f>F38/(120*$B38*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
       <c r="M38">
-        <f>G38/(120*$B38*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
       <c r="N38">
@@ -4830,11 +4823,11 @@
         <v>750</v>
       </c>
       <c r="F39">
-        <f>C39+D39</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G39">
-        <f>D39+E39</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H39">
@@ -4850,11 +4843,11 @@
         <v>1</v>
       </c>
       <c r="L39">
-        <f>F39/(120*$B39*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="M39">
-        <f>G39/(120*$B39*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="N39">
@@ -4938,11 +4931,11 @@
         <v>750</v>
       </c>
       <c r="F40">
-        <f>C40+D40</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G40">
-        <f>D40+E40</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H40">
@@ -4958,11 +4951,11 @@
         <v>1.125</v>
       </c>
       <c r="L40">
-        <f>F40/(120*$B40*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.875</v>
       </c>
       <c r="M40">
-        <f>G40/(120*$B40*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.875</v>
       </c>
       <c r="N40">
@@ -5046,11 +5039,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F41">
-        <f>C41+D41</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G41">
-        <f>D41+E41</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H41">
@@ -5066,11 +5059,11 @@
         <v>0.25</v>
       </c>
       <c r="L41">
-        <f>F41/(120*$B41*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="M41">
-        <f>G41/(120*$B41*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="N41">
@@ -5154,11 +5147,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F42">
-        <f>C42+D42</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G42">
-        <f>D42+E42</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H42">
@@ -5174,11 +5167,11 @@
         <v>0.26315789473684209</v>
       </c>
       <c r="L42">
-        <f>F42/(120*$B42*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.57894736842105265</v>
       </c>
       <c r="M42">
-        <f>G42/(120*$B42*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.57894736842105265</v>
       </c>
       <c r="N42">
@@ -5262,11 +5255,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F43">
-        <f>C43+D43</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G43">
-        <f>D43+E43</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H43">
@@ -5282,11 +5275,11 @@
         <v>0.27777777777777779</v>
       </c>
       <c r="L43">
-        <f>F43/(120*$B43*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.61111111111111116</v>
       </c>
       <c r="M43">
-        <f>G43/(120*$B43*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.61111111111111116</v>
       </c>
       <c r="N43">
@@ -5370,11 +5363,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F44">
-        <f>C44+D44</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G44">
-        <f>D44+E44</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H44">
@@ -5390,11 +5383,11 @@
         <v>0.29411764705882348</v>
       </c>
       <c r="L44">
-        <f>F44/(120*$B44*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.6470588235294118</v>
       </c>
       <c r="M44">
-        <f>G44/(120*$B44*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.6470588235294118</v>
       </c>
       <c r="N44">
@@ -5478,11 +5471,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F45">
-        <f>C45+D45</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G45">
-        <f>D45+E45</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H45">
@@ -5498,11 +5491,11 @@
         <v>0.31250000000000011</v>
       </c>
       <c r="L45">
-        <f>F45/(120*$B45*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.68750000000000011</v>
       </c>
       <c r="M45">
-        <f>G45/(120*$B45*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.68750000000000011</v>
       </c>
       <c r="N45">
@@ -5586,11 +5579,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F46">
-        <f>C46+D46</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G46">
-        <f>D46+E46</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H46">
@@ -5606,11 +5599,11 @@
         <v>0.33333333333333343</v>
       </c>
       <c r="L46">
-        <f>F46/(120*$B46*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.73333333333333339</v>
       </c>
       <c r="M46">
-        <f>G46/(120*$B46*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.73333333333333339</v>
       </c>
       <c r="N46">
@@ -5694,11 +5687,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F47">
-        <f>C47+D47</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G47">
-        <f>D47+E47</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H47">
@@ -5714,11 +5707,11 @@
         <v>0.35714285714285721</v>
       </c>
       <c r="L47">
-        <f>F47/(120*$B47*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.7857142857142857</v>
       </c>
       <c r="M47">
-        <f>G47/(120*$B47*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.7857142857142857</v>
       </c>
       <c r="N47">
@@ -5802,11 +5795,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F48">
-        <f>C48+D48</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G48">
-        <f>D48+E48</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H48">
@@ -5822,11 +5815,11 @@
         <v>0.38461538461538458</v>
       </c>
       <c r="L48">
-        <f>F48/(120*$B48*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.84615384615384626</v>
       </c>
       <c r="M48">
-        <f>G48/(120*$B48*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.84615384615384626</v>
       </c>
       <c r="N48">
@@ -5910,11 +5903,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F49">
-        <f>C49+D49</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G49">
-        <f>D49+E49</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H49">
@@ -5930,11 +5923,11 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="L49">
-        <f>F49/(120*$B49*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.91666666666666674</v>
       </c>
       <c r="M49">
-        <f>G49/(120*$B49*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.91666666666666674</v>
       </c>
       <c r="N49">
@@ -6018,11 +6011,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F50">
-        <f>C50+D50</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G50">
-        <f>D50+E50</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H50">
@@ -6038,11 +6031,11 @@
         <v>0.45454545454545459</v>
       </c>
       <c r="L50">
-        <f>F50/(120*$B50*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="M50">
-        <f>G50/(120*$B50*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="N50">
@@ -6126,11 +6119,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F51">
-        <f>C51+D51</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G51">
-        <f>D51+E51</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H51">
@@ -6146,11 +6139,11 @@
         <v>0.5</v>
       </c>
       <c r="L51">
-        <f>F51/(120*$B51*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="M51">
-        <f>G51/(120*$B51*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="N51">
@@ -6234,11 +6227,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F52">
-        <f>C52+D52</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G52">
-        <f>D52+E52</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H52">
@@ -6254,11 +6247,11 @@
         <v>0.55555555555555558</v>
       </c>
       <c r="L52">
-        <f>F52/(120*$B52*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.2222222222222223</v>
       </c>
       <c r="M52">
-        <f>G52/(120*$B52*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.2222222222222223</v>
       </c>
       <c r="N52">
@@ -6342,11 +6335,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F53">
-        <f>C53+D53</f>
+        <f t="shared" si="4"/>
         <v>916.66666666666674</v>
       </c>
       <c r="G53">
-        <f>D53+E53</f>
+        <f t="shared" si="5"/>
         <v>916.66666666666674</v>
       </c>
       <c r="H53">
@@ -6362,11 +6355,11 @@
         <v>0.62500000000000011</v>
       </c>
       <c r="L53">
-        <f>F53/(120*$B53*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.3750000000000002</v>
       </c>
       <c r="M53">
-        <f>G53/(120*$B53*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.3750000000000002</v>
       </c>
       <c r="N53">
@@ -6450,11 +6443,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F54">
-        <f>C54+D54</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G54">
-        <f>D54+E54</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H54">
@@ -6470,11 +6463,11 @@
         <v>0.25</v>
       </c>
       <c r="L54">
-        <f>F54/(120*$B54*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
       <c r="M54">
-        <f>G54/(120*$B54*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
       <c r="N54">
@@ -6558,11 +6551,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F55">
-        <f>C55+D55</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G55">
-        <f>D55+E55</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H55">
@@ -6578,11 +6571,11 @@
         <v>0.26315789473684209</v>
       </c>
       <c r="L55">
-        <f>F55/(120*$B55*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.78947368421052633</v>
       </c>
       <c r="M55">
-        <f>G55/(120*$B55*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.78947368421052633</v>
       </c>
       <c r="N55">
@@ -6666,11 +6659,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F56">
-        <f>C56+D56</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G56">
-        <f>D56+E56</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H56">
@@ -6686,11 +6679,11 @@
         <v>0.27777777777777779</v>
       </c>
       <c r="L56">
-        <f>F56/(120*$B56*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="M56">
-        <f>G56/(120*$B56*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="N56">
@@ -6774,11 +6767,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F57">
-        <f>C57+D57</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G57">
-        <f>D57+E57</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H57">
@@ -6794,11 +6787,11 @@
         <v>0.29411764705882348</v>
       </c>
       <c r="L57">
-        <f>F57/(120*$B57*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.88235294117647056</v>
       </c>
       <c r="M57">
-        <f>G57/(120*$B57*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.88235294117647056</v>
       </c>
       <c r="N57">
@@ -6882,11 +6875,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F58">
-        <f>C58+D58</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G58">
-        <f>D58+E58</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H58">
@@ -6902,11 +6895,11 @@
         <v>0.31250000000000011</v>
       </c>
       <c r="L58">
-        <f>F58/(120*$B58*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>0.9375</v>
       </c>
       <c r="M58">
-        <f>G58/(120*$B58*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>0.9375</v>
       </c>
       <c r="N58">
@@ -6990,11 +6983,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F59">
-        <f>C59+D59</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G59">
-        <f>D59+E59</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H59">
@@ -7010,11 +7003,11 @@
         <v>0.33333333333333343</v>
       </c>
       <c r="L59">
-        <f>F59/(120*$B59*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M59">
-        <f>G59/(120*$B59*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N59">
@@ -7098,11 +7091,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F60">
-        <f>C60+D60</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G60">
-        <f>D60+E60</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H60">
@@ -7118,11 +7111,11 @@
         <v>0.35714285714285721</v>
       </c>
       <c r="L60">
-        <f>F60/(120*$B60*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.0714285714285714</v>
       </c>
       <c r="M60">
-        <f>G60/(120*$B60*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.0714285714285714</v>
       </c>
       <c r="N60">
@@ -7206,11 +7199,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F61">
-        <f>C61+D61</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G61">
-        <f>D61+E61</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H61">
@@ -7226,11 +7219,11 @@
         <v>0.38461538461538458</v>
       </c>
       <c r="L61">
-        <f>F61/(120*$B61*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.153846153846154</v>
       </c>
       <c r="M61">
-        <f>G61/(120*$B61*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.153846153846154</v>
       </c>
       <c r="N61">
@@ -7314,11 +7307,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F62">
-        <f>C62+D62</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G62">
-        <f>D62+E62</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H62">
@@ -7334,11 +7327,11 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="L62">
-        <f>F62/(120*$B62*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.25</v>
       </c>
       <c r="M62">
-        <f>G62/(120*$B62*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.25</v>
       </c>
       <c r="N62">
@@ -7422,11 +7415,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F63">
-        <f>C63+D63</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G63">
-        <f>D63+E63</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H63">
@@ -7442,11 +7435,11 @@
         <v>0.45454545454545459</v>
       </c>
       <c r="L63">
-        <f>F63/(120*$B63*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.3636363636363638</v>
       </c>
       <c r="M63">
-        <f>G63/(120*$B63*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.3636363636363638</v>
       </c>
       <c r="N63">
@@ -7530,11 +7523,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F64">
-        <f>C64+D64</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G64">
-        <f>D64+E64</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H64">
@@ -7550,11 +7543,11 @@
         <v>0.5</v>
       </c>
       <c r="L64">
-        <f>F64/(120*$B64*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
       <c r="M64">
-        <f>G64/(120*$B64*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
       <c r="N64">
@@ -7638,11 +7631,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F65">
-        <f>C65+D65</f>
+        <f t="shared" si="4"/>
         <v>1250</v>
       </c>
       <c r="G65">
-        <f>D65+E65</f>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="H65">
@@ -7658,11 +7651,11 @@
         <v>0.55555555555555558</v>
       </c>
       <c r="L65">
-        <f>F65/(120*$B65*1000/3600)</f>
+        <f t="shared" si="6"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="M65">
-        <f>G65/(120*$B65*1000/3600)</f>
+        <f t="shared" si="7"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="N65">
@@ -7746,11 +7739,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F66">
-        <f>C66+D66</f>
+        <f t="shared" ref="F66:F97" si="8">C66+D66</f>
         <v>1250</v>
       </c>
       <c r="G66">
-        <f>D66+E66</f>
+        <f t="shared" ref="G66:G97" si="9">D66+E66</f>
         <v>1250</v>
       </c>
       <c r="H66">
@@ -7766,11 +7759,11 @@
         <v>0.62500000000000011</v>
       </c>
       <c r="L66">
-        <f>F66/(120*$B66*1000/3600)</f>
+        <f t="shared" ref="L66:L97" si="10">F66/(120*$B66*1000/3600)</f>
         <v>1.875</v>
       </c>
       <c r="M66">
-        <f>G66/(120*$B66*1000/3600)</f>
+        <f t="shared" ref="M66:M97" si="11">G66/(120*$B66*1000/3600)</f>
         <v>1.875</v>
       </c>
       <c r="N66">
@@ -7854,11 +7847,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F67">
-        <f>C67+D67</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G67">
-        <f>D67+E67</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H67">
@@ -7874,11 +7867,11 @@
         <v>0.35</v>
       </c>
       <c r="L67">
-        <f>F67/(120*$B67*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>0.85</v>
       </c>
       <c r="M67">
-        <f>G67/(120*$B67*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>0.85</v>
       </c>
       <c r="N67">
@@ -7962,11 +7955,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F68">
-        <f>C68+D68</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G68">
-        <f>D68+E68</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H68">
@@ -7982,11 +7975,11 @@
         <v>0.36842105263157898</v>
       </c>
       <c r="L68">
-        <f>F68/(120*$B68*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>0.89473684210526327</v>
       </c>
       <c r="M68">
-        <f>G68/(120*$B68*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>0.89473684210526327</v>
       </c>
       <c r="N68">
@@ -8070,11 +8063,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F69">
-        <f>C69+D69</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G69">
-        <f>D69+E69</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H69">
@@ -8090,11 +8083,11 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="L69">
-        <f>F69/(120*$B69*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>0.94444444444444453</v>
       </c>
       <c r="M69">
-        <f>G69/(120*$B69*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>0.94444444444444453</v>
       </c>
       <c r="N69">
@@ -8178,11 +8171,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F70">
-        <f>C70+D70</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G70">
-        <f>D70+E70</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H70">
@@ -8198,11 +8191,11 @@
         <v>0.41176470588235292</v>
       </c>
       <c r="L70">
-        <f>F70/(120*$B70*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="M70">
-        <f>G70/(120*$B70*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="N70">
@@ -8286,11 +8279,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F71">
-        <f>C71+D71</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G71">
-        <f>D71+E71</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H71">
@@ -8306,11 +8299,11 @@
         <v>0.43750000000000011</v>
       </c>
       <c r="L71">
-        <f>F71/(120*$B71*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.0625000000000002</v>
       </c>
       <c r="M71">
-        <f>G71/(120*$B71*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.0625000000000002</v>
       </c>
       <c r="N71">
@@ -8394,11 +8387,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F72">
-        <f>C72+D72</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G72">
-        <f>D72+E72</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H72">
@@ -8414,11 +8407,11 @@
         <v>0.46666666666666667</v>
       </c>
       <c r="L72">
-        <f>F72/(120*$B72*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.1333333333333333</v>
       </c>
       <c r="M72">
-        <f>G72/(120*$B72*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.1333333333333333</v>
       </c>
       <c r="N72">
@@ -8502,11 +8495,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F73">
-        <f>C73+D73</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G73">
-        <f>D73+E73</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H73">
@@ -8522,11 +8515,11 @@
         <v>0.5</v>
       </c>
       <c r="L73">
-        <f>F73/(120*$B73*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="M73">
-        <f>G73/(120*$B73*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="N73">
@@ -8610,11 +8603,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F74">
-        <f>C74+D74</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G74">
-        <f>D74+E74</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H74">
@@ -8630,11 +8623,11 @@
         <v>0.53846153846153855</v>
       </c>
       <c r="L74">
-        <f>F74/(120*$B74*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.3076923076923079</v>
       </c>
       <c r="M74">
-        <f>G74/(120*$B74*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.3076923076923079</v>
       </c>
       <c r="N74">
@@ -8718,11 +8711,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F75">
-        <f>C75+D75</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G75">
-        <f>D75+E75</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H75">
@@ -8738,11 +8731,11 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="L75">
-        <f>F75/(120*$B75*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.4166666666666667</v>
       </c>
       <c r="M75">
-        <f>G75/(120*$B75*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.4166666666666667</v>
       </c>
       <c r="N75">
@@ -8826,11 +8819,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F76">
-        <f>C76+D76</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G76">
-        <f>D76+E76</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H76">
@@ -8846,11 +8839,11 @@
         <v>0.63636363636363646</v>
       </c>
       <c r="L76">
-        <f>F76/(120*$B76*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.5454545454545456</v>
       </c>
       <c r="M76">
-        <f>G76/(120*$B76*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.5454545454545456</v>
       </c>
       <c r="N76">
@@ -8934,11 +8927,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F77">
-        <f>C77+D77</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G77">
-        <f>D77+E77</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H77">
@@ -8954,11 +8947,11 @@
         <v>0.70000000000000007</v>
       </c>
       <c r="L77">
-        <f>F77/(120*$B77*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.7</v>
       </c>
       <c r="M77">
-        <f>G77/(120*$B77*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.7</v>
       </c>
       <c r="N77">
@@ -9042,11 +9035,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F78">
-        <f>C78+D78</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G78">
-        <f>D78+E78</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H78">
@@ -9062,11 +9055,11 @@
         <v>0.77777777777777779</v>
       </c>
       <c r="L78">
-        <f>F78/(120*$B78*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.8888888888888891</v>
       </c>
       <c r="M78">
-        <f>G78/(120*$B78*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.8888888888888891</v>
       </c>
       <c r="N78">
@@ -9150,11 +9143,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F79">
-        <f>C79+D79</f>
+        <f t="shared" si="8"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="G79">
-        <f>D79+E79</f>
+        <f t="shared" si="9"/>
         <v>1416.6666666666667</v>
       </c>
       <c r="H79">
@@ -9170,11 +9163,11 @@
         <v>0.87500000000000011</v>
       </c>
       <c r="L79">
-        <f>F79/(120*$B79*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>2.1250000000000004</v>
       </c>
       <c r="M79">
-        <f>G79/(120*$B79*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>2.1250000000000004</v>
       </c>
       <c r="N79">
@@ -9258,11 +9251,11 @@
         <v>750</v>
       </c>
       <c r="F80">
-        <f>C80+D80</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G80">
-        <f>D80+E80</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H80">
@@ -9278,11 +9271,11 @@
         <v>0.45</v>
       </c>
       <c r="L80">
-        <f>F80/(120*$B80*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>0.95000000000000007</v>
       </c>
       <c r="M80">
-        <f>G80/(120*$B80*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>0.95000000000000007</v>
       </c>
       <c r="N80">
@@ -9366,11 +9359,11 @@
         <v>750</v>
       </c>
       <c r="F81">
-        <f>C81+D81</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G81">
-        <f>D81+E81</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H81">
@@ -9386,11 +9379,11 @@
         <v>0.47368421052631582</v>
       </c>
       <c r="L81">
-        <f>F81/(120*$B81*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="M81">
-        <f>G81/(120*$B81*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="N81">
@@ -9474,11 +9467,11 @@
         <v>750</v>
       </c>
       <c r="F82">
-        <f>C82+D82</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G82">
-        <f>D82+E82</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H82">
@@ -9494,11 +9487,11 @@
         <v>0.5</v>
       </c>
       <c r="L82">
-        <f>F82/(120*$B82*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.0555555555555556</v>
       </c>
       <c r="M82">
-        <f>G82/(120*$B82*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.0555555555555556</v>
       </c>
       <c r="N82">
@@ -9582,11 +9575,11 @@
         <v>750</v>
       </c>
       <c r="F83">
-        <f>C83+D83</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G83">
-        <f>D83+E83</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H83">
@@ -9602,11 +9595,11 @@
         <v>0.52941176470588236</v>
       </c>
       <c r="L83">
-        <f>F83/(120*$B83*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.1176470588235294</v>
       </c>
       <c r="M83">
-        <f>G83/(120*$B83*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.1176470588235294</v>
       </c>
       <c r="N83">
@@ -9690,11 +9683,11 @@
         <v>750</v>
       </c>
       <c r="F84">
-        <f>C84+D84</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G84">
-        <f>D84+E84</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H84">
@@ -9710,11 +9703,11 @@
         <v>0.5625</v>
       </c>
       <c r="L84">
-        <f>F84/(120*$B84*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.1875000000000002</v>
       </c>
       <c r="M84">
-        <f>G84/(120*$B84*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.1875000000000002</v>
       </c>
       <c r="N84">
@@ -9798,11 +9791,11 @@
         <v>750</v>
       </c>
       <c r="F85">
-        <f>C85+D85</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G85">
-        <f>D85+E85</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H85">
@@ -9818,11 +9811,11 @@
         <v>0.6</v>
       </c>
       <c r="L85">
-        <f>F85/(120*$B85*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.2666666666666668</v>
       </c>
       <c r="M85">
-        <f>G85/(120*$B85*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.2666666666666668</v>
       </c>
       <c r="N85">
@@ -9906,11 +9899,11 @@
         <v>750</v>
       </c>
       <c r="F86">
-        <f>C86+D86</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G86">
-        <f>D86+E86</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H86">
@@ -9926,11 +9919,11 @@
         <v>0.64285714285714279</v>
       </c>
       <c r="L86">
-        <f>F86/(120*$B86*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.3571428571428572</v>
       </c>
       <c r="M86">
-        <f>G86/(120*$B86*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.3571428571428572</v>
       </c>
       <c r="N86">
@@ -10014,11 +10007,11 @@
         <v>750</v>
       </c>
       <c r="F87">
-        <f>C87+D87</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G87">
-        <f>D87+E87</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H87">
@@ -10034,11 +10027,11 @@
         <v>0.6923076923076924</v>
       </c>
       <c r="L87">
-        <f>F87/(120*$B87*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.4615384615384617</v>
       </c>
       <c r="M87">
-        <f>G87/(120*$B87*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.4615384615384617</v>
       </c>
       <c r="N87">
@@ -10122,11 +10115,11 @@
         <v>750</v>
       </c>
       <c r="F88">
-        <f>C88+D88</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G88">
-        <f>D88+E88</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H88">
@@ -10142,11 +10135,11 @@
         <v>0.75</v>
       </c>
       <c r="L88">
-        <f>F88/(120*$B88*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.5833333333333335</v>
       </c>
       <c r="M88">
-        <f>G88/(120*$B88*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.5833333333333335</v>
       </c>
       <c r="N88">
@@ -10230,11 +10223,11 @@
         <v>750</v>
       </c>
       <c r="F89">
-        <f>C89+D89</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G89">
-        <f>D89+E89</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H89">
@@ -10250,11 +10243,11 @@
         <v>0.81818181818181823</v>
       </c>
       <c r="L89">
-        <f>F89/(120*$B89*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.7272727272727275</v>
       </c>
       <c r="M89">
-        <f>G89/(120*$B89*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.7272727272727275</v>
       </c>
       <c r="N89">
@@ -10338,11 +10331,11 @@
         <v>750</v>
       </c>
       <c r="F90">
-        <f>C90+D90</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G90">
-        <f>D90+E90</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H90">
@@ -10358,11 +10351,11 @@
         <v>0.89999999999999991</v>
       </c>
       <c r="L90">
-        <f>F90/(120*$B90*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>1.9000000000000001</v>
       </c>
       <c r="M90">
-        <f>G90/(120*$B90*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>1.9000000000000001</v>
       </c>
       <c r="N90">
@@ -10446,11 +10439,11 @@
         <v>750</v>
       </c>
       <c r="F91">
-        <f>C91+D91</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G91">
-        <f>D91+E91</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H91">
@@ -10466,11 +10459,11 @@
         <v>1</v>
       </c>
       <c r="L91">
-        <f>F91/(120*$B91*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>2.1111111111111112</v>
       </c>
       <c r="M91">
-        <f>G91/(120*$B91*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>2.1111111111111112</v>
       </c>
       <c r="N91">
@@ -10554,11 +10547,11 @@
         <v>750</v>
       </c>
       <c r="F92">
-        <f>C92+D92</f>
+        <f t="shared" si="8"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="G92">
-        <f>D92+E92</f>
+        <f t="shared" si="9"/>
         <v>1583.3333333333335</v>
       </c>
       <c r="H92">
@@ -10574,11 +10567,11 @@
         <v>1.125</v>
       </c>
       <c r="L92">
-        <f>F92/(120*$B92*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>2.3750000000000004</v>
       </c>
       <c r="M92">
-        <f>G92/(120*$B92*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>2.3750000000000004</v>
       </c>
       <c r="N92">
@@ -10662,11 +10655,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F93">
-        <f>C93+D93</f>
+        <f t="shared" si="8"/>
         <v>1250</v>
       </c>
       <c r="G93">
-        <f>D93+E93</f>
+        <f t="shared" si="9"/>
         <v>1250</v>
       </c>
       <c r="H93">
@@ -10682,11 +10675,11 @@
         <v>0.25</v>
       </c>
       <c r="L93">
-        <f>F93/(120*$B93*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>0.75</v>
       </c>
       <c r="M93">
-        <f>G93/(120*$B93*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>0.75</v>
       </c>
       <c r="N93">
@@ -10770,11 +10763,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F94">
-        <f>C94+D94</f>
+        <f t="shared" si="8"/>
         <v>1250</v>
       </c>
       <c r="G94">
-        <f>D94+E94</f>
+        <f t="shared" si="9"/>
         <v>1250</v>
       </c>
       <c r="H94">
@@ -10790,11 +10783,11 @@
         <v>0.26315789473684209</v>
       </c>
       <c r="L94">
-        <f>F94/(120*$B94*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>0.78947368421052633</v>
       </c>
       <c r="M94">
-        <f>G94/(120*$B94*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>0.78947368421052633</v>
       </c>
       <c r="N94">
@@ -10878,11 +10871,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F95">
-        <f>C95+D95</f>
+        <f t="shared" si="8"/>
         <v>1250</v>
       </c>
       <c r="G95">
-        <f>D95+E95</f>
+        <f t="shared" si="9"/>
         <v>1250</v>
       </c>
       <c r="H95">
@@ -10898,11 +10891,11 @@
         <v>0.27777777777777779</v>
       </c>
       <c r="L95">
-        <f>F95/(120*$B95*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="M95">
-        <f>G95/(120*$B95*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="N95">
@@ -10986,11 +10979,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F96">
-        <f>C96+D96</f>
+        <f t="shared" si="8"/>
         <v>1250</v>
       </c>
       <c r="G96">
-        <f>D96+E96</f>
+        <f t="shared" si="9"/>
         <v>1250</v>
       </c>
       <c r="H96">
@@ -11006,11 +10999,11 @@
         <v>0.29411764705882348</v>
       </c>
       <c r="L96">
-        <f>F96/(120*$B96*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>0.88235294117647056</v>
       </c>
       <c r="M96">
-        <f>G96/(120*$B96*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>0.88235294117647056</v>
       </c>
       <c r="N96">
@@ -11094,11 +11087,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F97">
-        <f>C97+D97</f>
+        <f t="shared" si="8"/>
         <v>1250</v>
       </c>
       <c r="G97">
-        <f>D97+E97</f>
+        <f t="shared" si="9"/>
         <v>1250</v>
       </c>
       <c r="H97">
@@ -11114,11 +11107,11 @@
         <v>0.31250000000000011</v>
       </c>
       <c r="L97">
-        <f>F97/(120*$B97*1000/3600)</f>
+        <f t="shared" si="10"/>
         <v>0.9375</v>
       </c>
       <c r="M97">
-        <f>G97/(120*$B97*1000/3600)</f>
+        <f t="shared" si="11"/>
         <v>0.9375</v>
       </c>
       <c r="N97">
@@ -11202,11 +11195,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F98">
-        <f>C98+D98</f>
+        <f t="shared" ref="F98:F129" si="12">C98+D98</f>
         <v>1250</v>
       </c>
       <c r="G98">
-        <f>D98+E98</f>
+        <f t="shared" ref="G98:G129" si="13">D98+E98</f>
         <v>1250</v>
       </c>
       <c r="H98">
@@ -11222,11 +11215,11 @@
         <v>0.33333333333333343</v>
       </c>
       <c r="L98">
-        <f>F98/(120*$B98*1000/3600)</f>
+        <f t="shared" ref="L98:L129" si="14">F98/(120*$B98*1000/3600)</f>
         <v>1</v>
       </c>
       <c r="M98">
-        <f>G98/(120*$B98*1000/3600)</f>
+        <f t="shared" ref="M98:M129" si="15">G98/(120*$B98*1000/3600)</f>
         <v>1</v>
       </c>
       <c r="N98">
@@ -11310,11 +11303,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F99">
-        <f>C99+D99</f>
+        <f t="shared" si="12"/>
         <v>1250</v>
       </c>
       <c r="G99">
-        <f>D99+E99</f>
+        <f t="shared" si="13"/>
         <v>1250</v>
       </c>
       <c r="H99">
@@ -11330,11 +11323,11 @@
         <v>0.35714285714285721</v>
       </c>
       <c r="L99">
-        <f>F99/(120*$B99*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1.0714285714285714</v>
       </c>
       <c r="M99">
-        <f>G99/(120*$B99*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1.0714285714285714</v>
       </c>
       <c r="N99">
@@ -11418,11 +11411,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F100">
-        <f>C100+D100</f>
+        <f t="shared" si="12"/>
         <v>1250</v>
       </c>
       <c r="G100">
-        <f>D100+E100</f>
+        <f t="shared" si="13"/>
         <v>1250</v>
       </c>
       <c r="H100">
@@ -11438,11 +11431,11 @@
         <v>0.38461538461538458</v>
       </c>
       <c r="L100">
-        <f>F100/(120*$B100*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1.153846153846154</v>
       </c>
       <c r="M100">
-        <f>G100/(120*$B100*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1.153846153846154</v>
       </c>
       <c r="N100">
@@ -11526,11 +11519,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F101">
-        <f>C101+D101</f>
+        <f t="shared" si="12"/>
         <v>1250</v>
       </c>
       <c r="G101">
-        <f>D101+E101</f>
+        <f t="shared" si="13"/>
         <v>1250</v>
       </c>
       <c r="H101">
@@ -11546,11 +11539,11 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="L101">
-        <f>F101/(120*$B101*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1.25</v>
       </c>
       <c r="M101">
-        <f>G101/(120*$B101*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1.25</v>
       </c>
       <c r="N101">
@@ -11634,11 +11627,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F102">
-        <f>C102+D102</f>
+        <f t="shared" si="12"/>
         <v>1250</v>
       </c>
       <c r="G102">
-        <f>D102+E102</f>
+        <f t="shared" si="13"/>
         <v>1250</v>
       </c>
       <c r="H102">
@@ -11654,11 +11647,11 @@
         <v>0.45454545454545459</v>
       </c>
       <c r="L102">
-        <f>F102/(120*$B102*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1.3636363636363638</v>
       </c>
       <c r="M102">
-        <f>G102/(120*$B102*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1.3636363636363638</v>
       </c>
       <c r="N102">
@@ -11742,11 +11735,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F103">
-        <f>C103+D103</f>
+        <f t="shared" si="12"/>
         <v>1250</v>
       </c>
       <c r="G103">
-        <f>D103+E103</f>
+        <f t="shared" si="13"/>
         <v>1250</v>
       </c>
       <c r="H103">
@@ -11762,11 +11755,11 @@
         <v>0.5</v>
       </c>
       <c r="L103">
-        <f>F103/(120*$B103*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1.5</v>
       </c>
       <c r="M103">
-        <f>G103/(120*$B103*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1.5</v>
       </c>
       <c r="N103">
@@ -11850,11 +11843,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F104">
-        <f>C104+D104</f>
+        <f t="shared" si="12"/>
         <v>1250</v>
       </c>
       <c r="G104">
-        <f>D104+E104</f>
+        <f t="shared" si="13"/>
         <v>1250</v>
       </c>
       <c r="H104">
@@ -11870,11 +11863,11 @@
         <v>0.55555555555555558</v>
       </c>
       <c r="L104">
-        <f>F104/(120*$B104*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="M104">
-        <f>G104/(120*$B104*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="N104">
@@ -11958,11 +11951,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F105">
-        <f>C105+D105</f>
+        <f t="shared" si="12"/>
         <v>1250</v>
       </c>
       <c r="G105">
-        <f>D105+E105</f>
+        <f t="shared" si="13"/>
         <v>1250</v>
       </c>
       <c r="H105">
@@ -11978,11 +11971,11 @@
         <v>0.62500000000000011</v>
       </c>
       <c r="L105">
-        <f>F105/(120*$B105*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1.875</v>
       </c>
       <c r="M105">
-        <f>G105/(120*$B105*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1.875</v>
       </c>
       <c r="N105">
@@ -12066,11 +12059,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F106">
-        <f>C106+D106</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G106">
-        <f>D106+E106</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H106">
@@ -12086,11 +12079,11 @@
         <v>0.25</v>
       </c>
       <c r="L106">
-        <f>F106/(120*$B106*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.5</v>
       </c>
       <c r="M106">
-        <f>G106/(120*$B106*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.5</v>
       </c>
       <c r="N106">
@@ -12174,11 +12167,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F107">
-        <f>C107+D107</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G107">
-        <f>D107+E107</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H107">
@@ -12194,11 +12187,11 @@
         <v>0.26315789473684209</v>
       </c>
       <c r="L107">
-        <f>F107/(120*$B107*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.52631578947368429</v>
       </c>
       <c r="M107">
-        <f>G107/(120*$B107*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.52631578947368429</v>
       </c>
       <c r="N107">
@@ -12282,11 +12275,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F108">
-        <f>C108+D108</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G108">
-        <f>D108+E108</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H108">
@@ -12302,11 +12295,11 @@
         <v>0.27777777777777779</v>
       </c>
       <c r="L108">
-        <f>F108/(120*$B108*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="M108">
-        <f>G108/(120*$B108*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="N108">
@@ -12390,11 +12383,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F109">
-        <f>C109+D109</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G109">
-        <f>D109+E109</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H109">
@@ -12410,11 +12403,11 @@
         <v>0.29411764705882348</v>
       </c>
       <c r="L109">
-        <f>F109/(120*$B109*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.58823529411764708</v>
       </c>
       <c r="M109">
-        <f>G109/(120*$B109*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.58823529411764708</v>
       </c>
       <c r="N109">
@@ -12498,11 +12491,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F110">
-        <f>C110+D110</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G110">
-        <f>D110+E110</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H110">
@@ -12518,11 +12511,11 @@
         <v>0.31250000000000011</v>
       </c>
       <c r="L110">
-        <f>F110/(120*$B110*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.62500000000000011</v>
       </c>
       <c r="M110">
-        <f>G110/(120*$B110*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.62500000000000011</v>
       </c>
       <c r="N110">
@@ -12606,11 +12599,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F111">
-        <f>C111+D111</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G111">
-        <f>D111+E111</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H111">
@@ -12626,11 +12619,11 @@
         <v>0.33333333333333343</v>
       </c>
       <c r="L111">
-        <f>F111/(120*$B111*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="M111">
-        <f>G111/(120*$B111*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="N111">
@@ -12714,11 +12707,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F112">
-        <f>C112+D112</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G112">
-        <f>D112+E112</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H112">
@@ -12734,11 +12727,11 @@
         <v>0.35714285714285721</v>
       </c>
       <c r="L112">
-        <f>F112/(120*$B112*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="M112">
-        <f>G112/(120*$B112*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="N112">
@@ -12822,11 +12815,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F113">
-        <f>C113+D113</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G113">
-        <f>D113+E113</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H113">
@@ -12842,11 +12835,11 @@
         <v>0.38461538461538458</v>
       </c>
       <c r="L113">
-        <f>F113/(120*$B113*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.76923076923076927</v>
       </c>
       <c r="M113">
-        <f>G113/(120*$B113*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.76923076923076927</v>
       </c>
       <c r="N113">
@@ -12930,11 +12923,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F114">
-        <f>C114+D114</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G114">
-        <f>D114+E114</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H114">
@@ -12950,11 +12943,11 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="L114">
-        <f>F114/(120*$B114*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="M114">
-        <f>G114/(120*$B114*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="N114">
@@ -13038,11 +13031,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F115">
-        <f>C115+D115</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G115">
-        <f>D115+E115</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H115">
@@ -13058,11 +13051,11 @@
         <v>0.45454545454545459</v>
       </c>
       <c r="L115">
-        <f>F115/(120*$B115*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.90909090909090917</v>
       </c>
       <c r="M115">
-        <f>G115/(120*$B115*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.90909090909090917</v>
       </c>
       <c r="N115">
@@ -13146,11 +13139,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F116">
-        <f>C116+D116</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G116">
-        <f>D116+E116</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H116">
@@ -13166,11 +13159,11 @@
         <v>0.5</v>
       </c>
       <c r="L116">
-        <f>F116/(120*$B116*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M116">
-        <f>G116/(120*$B116*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="N116">
@@ -13254,11 +13247,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F117">
-        <f>C117+D117</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G117">
-        <f>D117+E117</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H117">
@@ -13274,11 +13267,11 @@
         <v>0.55555555555555558</v>
       </c>
       <c r="L117">
-        <f>F117/(120*$B117*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="M117">
-        <f>G117/(120*$B117*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="N117">
@@ -13362,11 +13355,11 @@
         <v>416.66666666666669</v>
       </c>
       <c r="F118">
-        <f>C118+D118</f>
+        <f t="shared" si="12"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G118">
-        <f>D118+E118</f>
+        <f t="shared" si="13"/>
         <v>833.33333333333337</v>
       </c>
       <c r="H118">
@@ -13382,11 +13375,11 @@
         <v>0.62500000000000011</v>
       </c>
       <c r="L118">
-        <f>F118/(120*$B118*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1.2500000000000002</v>
       </c>
       <c r="M118">
-        <f>G118/(120*$B118*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1.2500000000000002</v>
       </c>
       <c r="N118">
@@ -13470,11 +13463,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F119">
-        <f>C119+D119</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="G119">
-        <f>D119+E119</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="H119">
@@ -13490,11 +13483,11 @@
         <v>0.35</v>
       </c>
       <c r="L119">
-        <f>F119/(120*$B119*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.6</v>
       </c>
       <c r="M119">
-        <f>G119/(120*$B119*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.6</v>
       </c>
       <c r="N119">
@@ -13578,11 +13571,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F120">
-        <f>C120+D120</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="G120">
-        <f>D120+E120</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="H120">
@@ -13598,11 +13591,11 @@
         <v>0.36842105263157898</v>
       </c>
       <c r="L120">
-        <f>F120/(120*$B120*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.63157894736842113</v>
       </c>
       <c r="M120">
-        <f>G120/(120*$B120*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.63157894736842113</v>
       </c>
       <c r="N120">
@@ -13686,11 +13679,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F121">
-        <f>C121+D121</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="G121">
-        <f>D121+E121</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="H121">
@@ -13706,11 +13699,11 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="L121">
-        <f>F121/(120*$B121*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="M121">
-        <f>G121/(120*$B121*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="N121">
@@ -13794,11 +13787,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F122">
-        <f>C122+D122</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="G122">
-        <f>D122+E122</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="H122">
@@ -13814,11 +13807,11 @@
         <v>0.41176470588235292</v>
       </c>
       <c r="L122">
-        <f>F122/(120*$B122*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.70588235294117641</v>
       </c>
       <c r="M122">
-        <f>G122/(120*$B122*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.70588235294117641</v>
       </c>
       <c r="N122">
@@ -13902,11 +13895,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F123">
-        <f>C123+D123</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="G123">
-        <f>D123+E123</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="H123">
@@ -13922,11 +13915,11 @@
         <v>0.43750000000000011</v>
       </c>
       <c r="L123">
-        <f>F123/(120*$B123*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.75</v>
       </c>
       <c r="M123">
-        <f>G123/(120*$B123*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.75</v>
       </c>
       <c r="N123">
@@ -14010,11 +14003,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F124">
-        <f>C124+D124</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="G124">
-        <f>D124+E124</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="H124">
@@ -14030,11 +14023,11 @@
         <v>0.46666666666666667</v>
       </c>
       <c r="L124">
-        <f>F124/(120*$B124*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.8</v>
       </c>
       <c r="M124">
-        <f>G124/(120*$B124*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.8</v>
       </c>
       <c r="N124">
@@ -14118,11 +14111,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F125">
-        <f>C125+D125</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="G125">
-        <f>D125+E125</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="H125">
@@ -14138,11 +14131,11 @@
         <v>0.5</v>
       </c>
       <c r="L125">
-        <f>F125/(120*$B125*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="M125">
-        <f>G125/(120*$B125*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="N125">
@@ -14226,11 +14219,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F126">
-        <f>C126+D126</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="G126">
-        <f>D126+E126</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="H126">
@@ -14246,11 +14239,11 @@
         <v>0.53846153846153855</v>
       </c>
       <c r="L126">
-        <f>F126/(120*$B126*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>0.92307692307692313</v>
       </c>
       <c r="M126">
-        <f>G126/(120*$B126*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>0.92307692307692313</v>
       </c>
       <c r="N126">
@@ -14334,11 +14327,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F127">
-        <f>C127+D127</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="G127">
-        <f>D127+E127</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="H127">
@@ -14354,11 +14347,11 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="L127">
-        <f>F127/(120*$B127*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M127">
-        <f>G127/(120*$B127*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="N127">
@@ -14442,11 +14435,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F128">
-        <f>C128+D128</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="G128">
-        <f>D128+E128</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="H128">
@@ -14462,11 +14455,11 @@
         <v>0.63636363636363646</v>
       </c>
       <c r="L128">
-        <f>F128/(120*$B128*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1.0909090909090911</v>
       </c>
       <c r="M128">
-        <f>G128/(120*$B128*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1.0909090909090911</v>
       </c>
       <c r="N128">
@@ -14550,11 +14543,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F129">
-        <f>C129+D129</f>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="G129">
-        <f>D129+E129</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="H129">
@@ -14570,11 +14563,11 @@
         <v>0.70000000000000007</v>
       </c>
       <c r="L129">
-        <f>F129/(120*$B129*1000/3600)</f>
+        <f t="shared" si="14"/>
         <v>1.2</v>
       </c>
       <c r="M129">
-        <f>G129/(120*$B129*1000/3600)</f>
+        <f t="shared" si="15"/>
         <v>1.2</v>
       </c>
       <c r="N129">
@@ -14658,11 +14651,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F130">
-        <f>C130+D130</f>
+        <f t="shared" ref="F130:F157" si="16">C130+D130</f>
         <v>1000</v>
       </c>
       <c r="G130">
-        <f>D130+E130</f>
+        <f t="shared" ref="G130:G157" si="17">D130+E130</f>
         <v>1000</v>
       </c>
       <c r="H130">
@@ -14678,11 +14671,11 @@
         <v>0.77777777777777779</v>
       </c>
       <c r="L130">
-        <f>F130/(120*$B130*1000/3600)</f>
+        <f t="shared" ref="L130:L157" si="18">F130/(120*$B130*1000/3600)</f>
         <v>1.3333333333333333</v>
       </c>
       <c r="M130">
-        <f>G130/(120*$B130*1000/3600)</f>
+        <f t="shared" ref="M130:M157" si="19">G130/(120*$B130*1000/3600)</f>
         <v>1.3333333333333333</v>
       </c>
       <c r="N130">
@@ -14766,11 +14759,11 @@
         <v>583.33333333333337</v>
       </c>
       <c r="F131">
-        <f>C131+D131</f>
+        <f t="shared" si="16"/>
         <v>1000</v>
       </c>
       <c r="G131">
-        <f>D131+E131</f>
+        <f t="shared" si="17"/>
         <v>1000</v>
       </c>
       <c r="H131">
@@ -14786,11 +14779,11 @@
         <v>0.87500000000000011</v>
       </c>
       <c r="L131">
-        <f>F131/(120*$B131*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>1.5</v>
       </c>
       <c r="M131">
-        <f>G131/(120*$B131*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.5</v>
       </c>
       <c r="N131">
@@ -14874,11 +14867,11 @@
         <v>750</v>
       </c>
       <c r="F132">
-        <f>C132+D132</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G132">
-        <f>D132+E132</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H132">
@@ -14894,11 +14887,11 @@
         <v>0.45</v>
       </c>
       <c r="L132">
-        <f>F132/(120*$B132*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="M132">
-        <f>G132/(120*$B132*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="N132">
@@ -14982,11 +14975,11 @@
         <v>750</v>
       </c>
       <c r="F133">
-        <f>C133+D133</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G133">
-        <f>D133+E133</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H133">
@@ -15002,11 +14995,11 @@
         <v>0.47368421052631582</v>
       </c>
       <c r="L133">
-        <f>F133/(120*$B133*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.73684210526315796</v>
       </c>
       <c r="M133">
-        <f>G133/(120*$B133*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>0.73684210526315796</v>
       </c>
       <c r="N133">
@@ -15090,11 +15083,11 @@
         <v>750</v>
       </c>
       <c r="F134">
-        <f>C134+D134</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G134">
-        <f>D134+E134</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H134">
@@ -15110,11 +15103,11 @@
         <v>0.5</v>
       </c>
       <c r="L134">
-        <f>F134/(120*$B134*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="M134">
-        <f>G134/(120*$B134*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="N134">
@@ -15198,11 +15191,11 @@
         <v>750</v>
       </c>
       <c r="F135">
-        <f>C135+D135</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G135">
-        <f>D135+E135</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H135">
@@ -15218,11 +15211,11 @@
         <v>0.52941176470588236</v>
       </c>
       <c r="L135">
-        <f>F135/(120*$B135*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.82352941176470584</v>
       </c>
       <c r="M135">
-        <f>G135/(120*$B135*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>0.82352941176470584</v>
       </c>
       <c r="N135">
@@ -15306,11 +15299,11 @@
         <v>750</v>
       </c>
       <c r="F136">
-        <f>C136+D136</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G136">
-        <f>D136+E136</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H136">
@@ -15326,11 +15319,11 @@
         <v>0.5625</v>
       </c>
       <c r="L136">
-        <f>F136/(120*$B136*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.87500000000000011</v>
       </c>
       <c r="M136">
-        <f>G136/(120*$B136*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>0.87500000000000011</v>
       </c>
       <c r="N136">
@@ -15414,11 +15407,11 @@
         <v>750</v>
       </c>
       <c r="F137">
-        <f>C137+D137</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G137">
-        <f>D137+E137</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H137">
@@ -15434,11 +15427,11 @@
         <v>0.6</v>
       </c>
       <c r="L137">
-        <f>F137/(120*$B137*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.93333333333333335</v>
       </c>
       <c r="M137">
-        <f>G137/(120*$B137*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>0.93333333333333335</v>
       </c>
       <c r="N137">
@@ -15522,11 +15515,11 @@
         <v>750</v>
       </c>
       <c r="F138">
-        <f>C138+D138</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G138">
-        <f>D138+E138</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H138">
@@ -15542,11 +15535,11 @@
         <v>0.64285714285714279</v>
       </c>
       <c r="L138">
-        <f>F138/(120*$B138*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="M138">
-        <f>G138/(120*$B138*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="N138">
@@ -15630,11 +15623,11 @@
         <v>750</v>
       </c>
       <c r="F139">
-        <f>C139+D139</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G139">
-        <f>D139+E139</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H139">
@@ -15650,11 +15643,11 @@
         <v>0.6923076923076924</v>
       </c>
       <c r="L139">
-        <f>F139/(120*$B139*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>1.0769230769230771</v>
       </c>
       <c r="M139">
-        <f>G139/(120*$B139*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.0769230769230771</v>
       </c>
       <c r="N139">
@@ -15738,11 +15731,11 @@
         <v>750</v>
       </c>
       <c r="F140">
-        <f>C140+D140</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G140">
-        <f>D140+E140</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H140">
@@ -15758,11 +15751,11 @@
         <v>0.75</v>
       </c>
       <c r="L140">
-        <f>F140/(120*$B140*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>1.1666666666666667</v>
       </c>
       <c r="M140">
-        <f>G140/(120*$B140*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.1666666666666667</v>
       </c>
       <c r="N140">
@@ -15846,11 +15839,11 @@
         <v>750</v>
       </c>
       <c r="F141">
-        <f>C141+D141</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G141">
-        <f>D141+E141</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H141">
@@ -15866,11 +15859,11 @@
         <v>0.81818181818181823</v>
       </c>
       <c r="L141">
-        <f>F141/(120*$B141*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>1.2727272727272729</v>
       </c>
       <c r="M141">
-        <f>G141/(120*$B141*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.2727272727272729</v>
       </c>
       <c r="N141">
@@ -15954,11 +15947,11 @@
         <v>750</v>
       </c>
       <c r="F142">
-        <f>C142+D142</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G142">
-        <f>D142+E142</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H142">
@@ -15974,11 +15967,11 @@
         <v>0.89999999999999991</v>
       </c>
       <c r="L142">
-        <f>F142/(120*$B142*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="M142">
-        <f>G142/(120*$B142*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="N142">
@@ -16062,11 +16055,11 @@
         <v>750</v>
       </c>
       <c r="F143">
-        <f>C143+D143</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G143">
-        <f>D143+E143</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H143">
@@ -16082,11 +16075,11 @@
         <v>1</v>
       </c>
       <c r="L143">
-        <f>F143/(120*$B143*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>1.5555555555555556</v>
       </c>
       <c r="M143">
-        <f>G143/(120*$B143*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.5555555555555556</v>
       </c>
       <c r="N143">
@@ -16170,11 +16163,11 @@
         <v>750</v>
       </c>
       <c r="F144">
-        <f>C144+D144</f>
+        <f t="shared" si="16"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="G144">
-        <f>D144+E144</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H144">
@@ -16190,11 +16183,11 @@
         <v>1.125</v>
       </c>
       <c r="L144">
-        <f>F144/(120*$B144*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>1.7500000000000002</v>
       </c>
       <c r="M144">
-        <f>G144/(120*$B144*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.7500000000000002</v>
       </c>
       <c r="N144">
@@ -16278,11 +16271,11 @@
         <v>750</v>
       </c>
       <c r="F145">
-        <f>C145+D145</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G145">
-        <f>D145+E145</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H145">
@@ -16298,11 +16291,11 @@
         <v>0.45</v>
       </c>
       <c r="L145">
-        <f>F145/(120*$B145*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
       <c r="M145">
-        <f>G145/(120*$B145*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="N145">
@@ -16386,11 +16379,11 @@
         <v>750</v>
       </c>
       <c r="F146">
-        <f>C146+D146</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G146">
-        <f>D146+E146</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H146">
@@ -16406,11 +16399,11 @@
         <v>0.47368421052631582</v>
       </c>
       <c r="L146">
-        <f>F146/(120*$B146*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.52631578947368429</v>
       </c>
       <c r="M146">
-        <f>G146/(120*$B146*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>0.73684210526315796</v>
       </c>
       <c r="N146">
@@ -16494,11 +16487,11 @@
         <v>750</v>
       </c>
       <c r="F147">
-        <f>C147+D147</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G147">
-        <f>D147+E147</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H147">
@@ -16514,11 +16507,11 @@
         <v>0.5</v>
       </c>
       <c r="L147">
-        <f>F147/(120*$B147*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="M147">
-        <f>G147/(120*$B147*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="N147">
@@ -16602,11 +16595,11 @@
         <v>750</v>
       </c>
       <c r="F148">
-        <f>C148+D148</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G148">
-        <f>D148+E148</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H148">
@@ -16622,11 +16615,11 @@
         <v>0.52941176470588236</v>
       </c>
       <c r="L148">
-        <f>F148/(120*$B148*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.58823529411764708</v>
       </c>
       <c r="M148">
-        <f>G148/(120*$B148*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>0.82352941176470584</v>
       </c>
       <c r="N148">
@@ -16710,11 +16703,11 @@
         <v>750</v>
       </c>
       <c r="F149">
-        <f>C149+D149</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G149">
-        <f>D149+E149</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H149">
@@ -16730,11 +16723,11 @@
         <v>0.5625</v>
       </c>
       <c r="L149">
-        <f>F149/(120*$B149*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.62500000000000011</v>
       </c>
       <c r="M149">
-        <f>G149/(120*$B149*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>0.87500000000000011</v>
       </c>
       <c r="N149">
@@ -16818,11 +16811,11 @@
         <v>750</v>
       </c>
       <c r="F150">
-        <f>C150+D150</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G150">
-        <f>D150+E150</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H150">
@@ -16838,11 +16831,11 @@
         <v>0.6</v>
       </c>
       <c r="L150">
-        <f>F150/(120*$B150*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="M150">
-        <f>G150/(120*$B150*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>0.93333333333333335</v>
       </c>
       <c r="N150">
@@ -16926,11 +16919,11 @@
         <v>750</v>
       </c>
       <c r="F151">
-        <f>C151+D151</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G151">
-        <f>D151+E151</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H151">
@@ -16946,11 +16939,11 @@
         <v>0.64285714285714279</v>
       </c>
       <c r="L151">
-        <f>F151/(120*$B151*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="M151">
-        <f>G151/(120*$B151*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="N151">
@@ -17034,11 +17027,11 @@
         <v>750</v>
       </c>
       <c r="F152">
-        <f>C152+D152</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G152">
-        <f>D152+E152</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H152">
@@ -17054,11 +17047,11 @@
         <v>0.6923076923076924</v>
       </c>
       <c r="L152">
-        <f>F152/(120*$B152*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.76923076923076927</v>
       </c>
       <c r="M152">
-        <f>G152/(120*$B152*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.0769230769230771</v>
       </c>
       <c r="N152">
@@ -17142,11 +17135,11 @@
         <v>750</v>
       </c>
       <c r="F153">
-        <f>C153+D153</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G153">
-        <f>D153+E153</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H153">
@@ -17162,11 +17155,11 @@
         <v>0.75</v>
       </c>
       <c r="L153">
-        <f>F153/(120*$B153*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="M153">
-        <f>G153/(120*$B153*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.1666666666666667</v>
       </c>
       <c r="N153">
@@ -17250,11 +17243,11 @@
         <v>750</v>
       </c>
       <c r="F154">
-        <f>C154+D154</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G154">
-        <f>D154+E154</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H154">
@@ -17270,11 +17263,11 @@
         <v>0.81818181818181823</v>
       </c>
       <c r="L154">
-        <f>F154/(120*$B154*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>0.90909090909090917</v>
       </c>
       <c r="M154">
-        <f>G154/(120*$B154*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.2727272727272729</v>
       </c>
       <c r="N154">
@@ -17358,11 +17351,11 @@
         <v>750</v>
       </c>
       <c r="F155">
-        <f>C155+D155</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G155">
-        <f>D155+E155</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H155">
@@ -17378,11 +17371,11 @@
         <v>0.89999999999999991</v>
       </c>
       <c r="L155">
-        <f>F155/(120*$B155*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="M155">
-        <f>G155/(120*$B155*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="N155">
@@ -17466,11 +17459,11 @@
         <v>750</v>
       </c>
       <c r="F156">
-        <f>C156+D156</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G156">
-        <f>D156+E156</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H156">
@@ -17486,11 +17479,11 @@
         <v>1</v>
       </c>
       <c r="L156">
-        <f>F156/(120*$B156*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="M156">
-        <f>G156/(120*$B156*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.5555555555555556</v>
       </c>
       <c r="N156">
@@ -17574,11 +17567,11 @@
         <v>750</v>
       </c>
       <c r="F157">
-        <f>C157+D157</f>
+        <f t="shared" si="16"/>
         <v>833.33333333333337</v>
       </c>
       <c r="G157">
-        <f>D157+E157</f>
+        <f t="shared" si="17"/>
         <v>1166.6666666666667</v>
       </c>
       <c r="H157">
@@ -17594,11 +17587,11 @@
         <v>1.125</v>
       </c>
       <c r="L157">
-        <f>F157/(120*$B157*1000/3600)</f>
+        <f t="shared" si="18"/>
         <v>1.2500000000000002</v>
       </c>
       <c r="M157">
-        <f>G157/(120*$B157*1000/3600)</f>
+        <f t="shared" si="19"/>
         <v>1.7500000000000002</v>
       </c>
       <c r="N157">
@@ -17668,85 +17661,77 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="I2:I157">
-    <cfRule type="cellIs" dxfId="17" priority="21" operator="between">
+    <cfRule type="cellIs" dxfId="15" priority="20" operator="between">
+      <formula>0.95</formula>
+      <formula>1.05</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="21" operator="between">
       <formula>0.45</formula>
       <formula>0.55</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="20" operator="between">
-      <formula>0.95</formula>
-      <formula>1.05</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J157">
-    <cfRule type="cellIs" dxfId="15" priority="19" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="18" operator="between">
+      <formula>0.85</formula>
+      <formula>1.15</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="19" operator="between">
       <formula>0.35</formula>
       <formula>0.65</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="18" operator="between">
-      <formula>0.85</formula>
-      <formula>1.15</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:L157">
+    <cfRule type="cellIs" dxfId="11" priority="14" operator="between">
+      <formula>0.9</formula>
+      <formula>1.1</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K157">
-    <cfRule type="cellIs" dxfId="13" priority="17" operator="between">
+    <cfRule type="cellIs" dxfId="10" priority="15" operator="between">
       <formula>0.4</formula>
       <formula>0.6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="16" operator="between">
-      <formula>0.9</formula>
-      <formula>1.1</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L157">
-    <cfRule type="cellIs" dxfId="11" priority="15" operator="between">
-      <formula>0.4</formula>
-      <formula>0.6</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="14" operator="between">
-      <formula>0.9</formula>
-      <formula>1.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="13" operator="between">
-      <formula>1.4</formula>
-      <formula>1.6</formula>
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="between">
+      <formula>2.4</formula>
+      <formula>2.6</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="8" priority="12" operator="between">
       <formula>1.9</formula>
       <formula>2.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="11" operator="between">
-      <formula>2.4</formula>
-      <formula>2.6</formula>
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="between">
+      <formula>1.4</formula>
+      <formula>1.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M157">
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="between">
-      <formula>0.45</formula>
-      <formula>0.55</formula>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="between">
+      <formula>2.45</formula>
+      <formula>2.55</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="between">
-      <formula>0.95</formula>
-      <formula>1.05</formula>
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="between">
+      <formula>1.95</formula>
+      <formula>2.05</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="4" priority="8" operator="between">
       <formula>1.45</formula>
       <formula>1.55</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="between">
-      <formula>1.95</formula>
-      <formula>2.05</formula>
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="between">
+      <formula>0.95</formula>
+      <formula>1.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="between">
-      <formula>2.45</formula>
-      <formula>2.55</formula>
+    <cfRule type="cellIs" dxfId="2" priority="10" operator="between">
+      <formula>0.45</formula>
+      <formula>0.55</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N157">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>OR(N2=0.25, N2=0.75, N2=1.25, N2=1.75, N2=2.25, N2=2.75, N2=3.25, N2=3.75)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>OR(N2=0.5, N2=1, N2=1.5, N2=2, N2=2.5, N2=3, N2=3.5, N2=4)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>OR(N2=0.25, N2=0.75, N2=1.25, N2=1.75, N2=2.25, N2=2.75, N2=3.25, N2=3.75)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/signal_coodination/results_final.xlsx
+++ b/signal_coodination/results_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50a7229fe28fb870/デスクトップ/randy_utokyo/signal_coodination/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hibik\github\randy_utokyo\signal_coodination\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{85338E4B-D322-4E00-93A8-6F59D7BF7565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A21DCCEA-FF35-46DC-916A-3C3BC05DC2AE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2811DD-6ABC-495A-87AA-95753DC710EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -450,10 +472,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -740,28 +758,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AQ157"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" customWidth="1"/>
+    <col min="6" max="6" width="9.21875" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" customWidth="1"/>
     <col min="14" max="23" width="10" customWidth="1"/>
-    <col min="28" max="28" width="15.54296875" customWidth="1"/>
-    <col min="29" max="30" width="15.1796875" customWidth="1"/>
-    <col min="31" max="31" width="14.90625" customWidth="1"/>
-    <col min="32" max="32" width="13.6328125" customWidth="1"/>
-    <col min="33" max="33" width="13.54296875" customWidth="1"/>
-    <col min="34" max="34" width="12.54296875" customWidth="1"/>
-    <col min="35" max="35" width="18.08984375" customWidth="1"/>
-    <col min="36" max="39" width="13.453125" customWidth="1"/>
-    <col min="40" max="40" width="12.54296875" customWidth="1"/>
-    <col min="41" max="41" width="13.453125" customWidth="1"/>
-    <col min="42" max="42" width="12.1796875" customWidth="1"/>
-    <col min="43" max="43" width="15.36328125" customWidth="1"/>
+    <col min="28" max="28" width="15.5546875" customWidth="1"/>
+    <col min="29" max="30" width="15.21875" customWidth="1"/>
+    <col min="31" max="31" width="14.88671875" customWidth="1"/>
+    <col min="32" max="32" width="13.6640625" customWidth="1"/>
+    <col min="33" max="33" width="13.5546875" customWidth="1"/>
+    <col min="34" max="34" width="12.5546875" customWidth="1"/>
+    <col min="35" max="35" width="18.109375" customWidth="1"/>
+    <col min="36" max="39" width="13.44140625" customWidth="1"/>
+    <col min="40" max="40" width="12.5546875" customWidth="1"/>
+    <col min="41" max="41" width="13.44140625" customWidth="1"/>
+    <col min="42" max="42" width="12.21875" customWidth="1"/>
+    <col min="43" max="43" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.2">
@@ -8073,9 +8092,9 @@
         <f t="shared" si="16"/>
         <v>1250</v>
       </c>
-      <c r="H51">
-        <f t="shared" si="4"/>
-        <v>1666.6666666666667</v>
+      <c r="H51" t="e" cm="1">
+        <f t="array" aca="1" ref="H51" ca="1">I103SUM(C51:E51)</f>
+        <v>#NAME?</v>
       </c>
       <c r="I51">
         <v>0.5</v>
@@ -15819,7 +15838,7 @@
         <v>0.55555555555555558</v>
       </c>
       <c r="J104">
-        <v>1.1111111111111109</v>
+        <v>1.1111111111111101</v>
       </c>
       <c r="K104">
         <v>1</v>
@@ -15834,7 +15853,7 @@
       </c>
       <c r="N104">
         <f t="shared" si="24"/>
-        <v>2.6666666666666665</v>
+        <v>2.6666666666666656</v>
       </c>
       <c r="O104">
         <f t="shared" si="25"/>
@@ -15858,11 +15877,11 @@
       </c>
       <c r="T104">
         <f t="shared" si="30"/>
-        <v>0.16666666666666652</v>
+        <v>0.16666666666666563</v>
       </c>
       <c r="U104">
         <f t="shared" si="31"/>
-        <v>0.16675923355337358</v>
+        <v>0.16675923355337269</v>
       </c>
       <c r="V104">
         <f t="shared" si="32"/>
@@ -15870,7 +15889,7 @@
       </c>
       <c r="W104">
         <f t="shared" si="33"/>
-        <v>0.18962275739862228</v>
+        <v>0.1896227573986215</v>
       </c>
       <c r="X104">
         <v>0</v>
@@ -23756,11 +23775,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFD0299-BB08-4572-A462-6844188D7A6E}">
   <dimension ref="A1:AH158"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="23" max="23" width="11.90625" customWidth="1"/>
-    <col min="24" max="24" width="14.453125" customWidth="1"/>
+    <col min="23" max="23" width="11.88671875" customWidth="1"/>
+    <col min="24" max="24" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.2">

--- a/signal_coodination/results_final.xlsx
+++ b/signal_coodination/results_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hibik\github\randy_utokyo\signal_coodination\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2811DD-6ABC-495A-87AA-95753DC710EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBD30DE-4F90-4EF0-9832-906E51A6BB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
